--- a/artfynd/A 26363-2023 artfynd.xlsx
+++ b/artfynd/A 26363-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117562085</v>
+        <v>117561641</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494099</v>
+        <v>494093</v>
       </c>
       <c r="R2" t="n">
-        <v>6937379</v>
+        <v>6937216</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117561956</v>
+        <v>117561878</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494125</v>
+        <v>494121</v>
       </c>
       <c r="R3" t="n">
-        <v>6937348</v>
+        <v>6937276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117561641</v>
+        <v>117562130</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494093</v>
+        <v>494099</v>
       </c>
       <c r="R4" t="n">
-        <v>6937216</v>
+        <v>6937380</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117562285</v>
+        <v>117562085</v>
       </c>
       <c r="B5" t="n">
-        <v>78217</v>
+        <v>79561</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494065</v>
+        <v>494099</v>
       </c>
       <c r="R5" t="n">
-        <v>6937419</v>
+        <v>6937379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117562153</v>
+        <v>117561956</v>
       </c>
       <c r="B6" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494098</v>
+        <v>494125</v>
       </c>
       <c r="R6" t="n">
-        <v>6937380</v>
+        <v>6937348</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117561878</v>
+        <v>117562285</v>
       </c>
       <c r="B7" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494121</v>
+        <v>494065</v>
       </c>
       <c r="R7" t="n">
-        <v>6937276</v>
+        <v>6937419</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117562130</v>
+        <v>117562153</v>
       </c>
       <c r="B8" t="n">
-        <v>79561</v>
+        <v>78514</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494099</v>
+        <v>494098</v>
       </c>
       <c r="R8" t="n">
         <v>6937380</v>

--- a/artfynd/A 26363-2023 artfynd.xlsx
+++ b/artfynd/A 26363-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117561641</v>
+        <v>117561878</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494093</v>
+        <v>494121</v>
       </c>
       <c r="R2" t="n">
-        <v>6937216</v>
+        <v>6937276</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117561878</v>
+        <v>117561641</v>
       </c>
       <c r="B3" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494121</v>
+        <v>494093</v>
       </c>
       <c r="R3" t="n">
-        <v>6937276</v>
+        <v>6937216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117562130</v>
+        <v>117561956</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>78482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494099</v>
+        <v>494125</v>
       </c>
       <c r="R4" t="n">
-        <v>6937380</v>
+        <v>6937348</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117562085</v>
+        <v>117562153</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>78516</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494099</v>
+        <v>494098</v>
       </c>
       <c r="R5" t="n">
-        <v>6937379</v>
+        <v>6937380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117561956</v>
+        <v>117562085</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494125</v>
+        <v>494099</v>
       </c>
       <c r="R6" t="n">
-        <v>6937348</v>
+        <v>6937379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1238,7 @@
         <v>117562285</v>
       </c>
       <c r="B7" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117562153</v>
+        <v>117562130</v>
       </c>
       <c r="B8" t="n">
-        <v>78514</v>
+        <v>79563</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494098</v>
+        <v>494099</v>
       </c>
       <c r="R8" t="n">
         <v>6937380</v>
@@ -1462,7 +1462,7 @@
         <v>117684928</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>117734582</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 26363-2023 artfynd.xlsx
+++ b/artfynd/A 26363-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562153</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684546</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117685602</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117561641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117561841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117561956</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562673</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684928</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117561878</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562632</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117685349</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117685481</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562707</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562846</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117734582</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2506,6 +2591,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117734596</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2613,6 +2703,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562285</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2720,6 +2815,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562427</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2827,8 +2927,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117720982</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>